--- a/preorder_forms/025_headphone_line_pre_order_form--preorder_forms.xlsx
+++ b/preorder_forms/025_headphone_line_pre_order_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Shipping Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Shipping Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Shipping Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_121,_'name':_'online_payment',_'label':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 121, 'name': 'Online Payment', 'label': 'Online Payment'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_122,_'name':_'offline_payment',_'label':_'offline_payment'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 122, 'name': 'Offline Payment', 'label': 'Offline Payment'}</t>
+          <t>Offline Payment</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_131,_'name':_'pre-order_available',_'label':_'pre-order_available'}</t>
+          <t>pre-order_available</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 131, 'name': 'Pre-Order Available', 'label': 'Pre-Order Available'}</t>
+          <t>Pre-Order Available</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_132,_'name':_'pre-order_sold_out',_'label':_'pre-order_sold_out'}</t>
+          <t>pre-order_sold_out</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 132, 'name': 'Pre-Order Sold Out', 'label': 'Pre-Order Sold Out'}</t>
+          <t>Pre-Order Sold Out</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_133,_'label':_'pre-order_canceled'}</t>
+          <t>pre-order_canceled</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 133, 'label': 'Pre-Order Canceled'}</t>
+          <t>Pre-Order Canceled</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_134,_'label':_'pre-order_not_available'}</t>
+          <t>pre-order_not_available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 134, 'label': 'Pre-Order Not Available'}</t>
+          <t>Pre-Order Not Available</t>
         </is>
       </c>
     </row>
